--- a/data/templates/cdp_sme_questionnaire.xlsx
+++ b/data/templates/cdp_sme_questionnaire.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Climate module" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,7 +35,15 @@
       <color rgb="00555555"/>
     </font>
     <font>
+      <color rgb="00777777"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00888888"/>
     </font>
   </fonts>
   <fills count="4">
@@ -67,16 +76,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,348 +459,405 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="84" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supplier Climate Questionnaire — SME (aligned to CDP 2026 SME climate data points)</t>
+          <t>CDP SME climate questions — offline answer sheet</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Please answer in column C. Leave a cell blank if the data is unavailable and explain in column D.</t>
+          <t>CDP itself is answered on the CDP Portal; this is the offline sheet buyers circulate. Question numbers and wording are CDP's own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Source: 2024 SME Questionnaire and Reporting Guidance, Modules 14-21, version 1.0 (released 30 April 2024). https://cdn.cdp.net/cdp-production/comfy/cms/files/files/000/009/090/original/CDP_2024_SME_Questionnaire_-_PDF_export.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Notes / evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Module 14: SME Introduction</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>State the end date of the year for which you are reporting data.</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Select the countries/areas in which the entities reported in 14.5 are based and/or conduct business.</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Module 20: SME Emissions</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Select the name of the standard, protocol, or methodology you have used to collect activity data and calculate emissions.</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>What were your organization’s gross global Scope 1 emissions in metric tons CO2e?</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>answer in the rows below</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Gross global Scope 1 emissions (metric tons CO2e)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Methodological details</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>What were your organization’s gross global Scope 2 emissions in metric tons CO2e?</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>answer in the rows below</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Gross global Scope 2, location-based emissions (metric tons CO2e)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Gross global Scope 2, market-based emissions (metric tons CO2e)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Methodological details</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Account for your organization’s gross global Scope 3 emissions, disclosing and explaining any exclusions.</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Indicate the verification/assurance status that applies to your reported emissions.</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>How do your gross global emissions (Scope 1 and 2 combined) for the reporting year compare to those of the previous reporting year?</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>20.12</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Allocate your emissions to your customers listed below according to the goods or services you have sold them in this reporting period.</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>20.15.2</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Report your organization’s consumption of purchased or acquired electricity in MWh.</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>answer in the rows below</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>MWh from renewable sources</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Total (renewable + non-renewable) MWh</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>20.16</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Did you have an emissions or other climate-related target that was active in the reporting year?</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>20.17</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Did you have emissions reduction initiatives that were active within the reporting year? Note that this can include those in the planning and/or implementation phases.</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="C19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Lists!$A$1:$A$2</formula1>
+    </dataValidation>
+    <dataValidation sqref="C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Lists!$B$1:$B$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="C26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Lists!$C$1:$C$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>No third-party verification or assurance</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Increased</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Third-party verification or assurance process in place</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Decreased</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No, but we plan to within the next two years</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Remained the same overall</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>No, and we do not plan to within the next two years</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Notes / evidence</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Supplier information</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Organisation name</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Country of headquarters</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Reporting period (start and end dates)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Sites included in this response</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Emissions</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>What were your organisation's gross global Scope 1 emissions in metric tons CO2e?</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>20.5a</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>What were your organisation's gross global Scope 2 emissions (location-based) in metric tons CO2e?</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>20.5b</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>What were your organisation's gross global Scope 2 emissions (market-based) in metric tons CO2e?</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>20.6</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Describe the methodology, standards and emission factors used to calculate Scope 1 and 2</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>If available, provide your Scope 3 emissions in metric tons CO2e and the categories covered</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Are your Scope 1 and 2 emissions verified by a third party? State the standard and assurance level</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>20.15.2</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Total electricity consumed in the reporting year (MWh)</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>20.15.3</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Total fuel consumed in the reporting year, by fuel type and unit</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Intensity and allocation</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>20.12a</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Scope 1+2 emissions intensity per unit of revenue (tCO2e per million, state currency)</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>20.12b</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Emissions allocated to the requesting customer (tCO2e) and the allocation method used</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Targets and actions</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>20.16</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Do you have an emissions reduction target? Describe it</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>20.17</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Describe emission reduction activities undertaken or planned</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="n"/>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Data quality</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>DQ.1</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Describe the share of primary (metered/invoiced) versus estimated data in your Scope 1 and 2 figures</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>This is our first year of reporting, so we cannot compare to last year</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
